--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="375">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -850,6 +850,10 @@
   </si>
   <si>
     <t>Resultat av åtgärd. Data i form av bifogade bilder eller liknande.</t>
+  </si>
+  <si>
+    <t>getreferraloutcome-actresult-choice:Ett och endast ett av value och reference ska anges {value.exists() xor reference.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMReferralOutcome.referralOutcome.referralOutcomeBody.act.actResult.id</t>
@@ -9475,15 +9479,15 @@
         <v>72</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9580,10 +9584,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9682,10 +9686,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9786,10 +9790,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9815,7 +9819,7 @@
         <v>113</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>195</v>
@@ -9869,7 +9873,7 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>73</v>
@@ -9886,10 +9890,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9915,10 +9919,10 @@
         <v>113</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9969,7 +9973,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -9986,10 +9990,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10012,13 +10016,13 @@
         <v>72</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10069,7 +10073,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10086,10 +10090,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10112,13 +10116,13 @@
         <v>72</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10169,7 +10173,7 @@
         <v>72</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
@@ -10186,10 +10190,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10215,10 +10219,10 @@
         <v>78</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10269,7 +10273,7 @@
         <v>72</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -10286,10 +10290,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10386,10 +10390,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10488,10 +10492,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10592,10 +10596,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10621,10 +10625,10 @@
         <v>113</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10675,7 +10679,7 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -10692,10 +10696,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10721,10 +10725,10 @@
         <v>113</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10775,7 +10779,7 @@
         <v>72</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -10792,10 +10796,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10821,10 +10825,10 @@
         <v>123</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10875,7 +10879,7 @@
         <v>72</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
@@ -10892,10 +10896,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10921,10 +10925,10 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10975,7 +10979,7 @@
         <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -10992,10 +10996,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11092,10 +11096,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11194,10 +11198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11298,10 +11302,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11327,10 +11331,10 @@
         <v>123</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11381,7 +11385,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -11398,10 +11402,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11430,7 +11434,7 @@
         <v>188</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11481,7 +11485,7 @@
         <v>72</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -11498,10 +11502,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11581,7 +11585,7 @@
         <v>72</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -11598,10 +11602,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11630,7 +11634,7 @@
         <v>147</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11681,7 +11685,7 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>73</v>
@@ -11698,10 +11702,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11727,7 +11731,7 @@
         <v>78</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>151</v>
@@ -11781,7 +11785,7 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -11798,10 +11802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11898,10 +11902,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12000,10 +12004,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12104,10 +12108,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12133,7 +12137,7 @@
         <v>113</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>157</v>
@@ -12187,7 +12191,7 @@
         <v>72</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>73</v>
@@ -12204,10 +12208,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12233,7 +12237,7 @@
         <v>113</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M107" t="s" s="2">
         <v>160</v>
@@ -12287,7 +12291,7 @@
         <v>72</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>73</v>
@@ -12304,10 +12308,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12387,7 +12391,7 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>73</v>
@@ -12404,10 +12408,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12433,7 +12437,7 @@
         <v>113</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>166</v>
@@ -12487,7 +12491,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -12504,10 +12508,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12533,7 +12537,7 @@
         <v>113</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>169</v>
@@ -12587,7 +12591,7 @@
         <v>72</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -12604,10 +12608,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12633,7 +12637,7 @@
         <v>113</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M111" t="s" s="2">
         <v>172</v>
@@ -12687,7 +12691,7 @@
         <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12704,10 +12708,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12733,7 +12737,7 @@
         <v>113</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M112" t="s" s="2">
         <v>195</v>
@@ -12787,7 +12791,7 @@
         <v>72</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>73</v>
@@ -12804,10 +12808,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12833,7 +12837,7 @@
         <v>113</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>195</v>
@@ -12887,7 +12891,7 @@
         <v>72</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>73</v>
@@ -12904,10 +12908,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12936,7 +12940,7 @@
         <v>201</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -12987,7 +12991,7 @@
         <v>72</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>73</v>
@@ -13004,10 +13008,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13033,10 +13037,10 @@
         <v>78</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13087,7 +13091,7 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>73</v>
@@ -13104,10 +13108,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13204,10 +13208,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13306,10 +13310,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13410,10 +13414,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13439,10 +13443,10 @@
         <v>123</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -13493,7 +13497,7 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -13510,10 +13514,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13539,10 +13543,10 @@
         <v>113</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13593,7 +13597,7 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>73</v>
@@ -13610,10 +13614,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13639,10 +13643,10 @@
         <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13693,7 +13697,7 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>73</v>
@@ -13710,10 +13714,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13739,10 +13743,10 @@
         <v>78</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13793,7 +13797,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -13810,10 +13814,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13910,10 +13914,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14012,10 +14016,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14116,10 +14120,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14145,10 +14149,10 @@
         <v>113</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14199,7 +14203,7 @@
         <v>72</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -14216,10 +14220,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14245,10 +14249,10 @@
         <v>113</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14299,7 +14303,7 @@
         <v>72</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>73</v>
@@ -14316,10 +14320,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14345,10 +14349,10 @@
         <v>113</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14399,7 +14403,7 @@
         <v>72</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -14416,10 +14420,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14445,10 +14449,10 @@
         <v>113</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14499,7 +14503,7 @@
         <v>72</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>73</v>
@@ -14516,10 +14520,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14545,10 +14549,10 @@
         <v>113</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14599,7 +14603,7 @@
         <v>72</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
